--- a/PTA/Truist/12-08-25-Truist-Partials-Entries-Converted-to-Applications.xlsx
+++ b/PTA/Truist/12-08-25-Truist-Partials-Entries-Converted-to-Applications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilia\PycharmProjects\WatsonInstitute\PTA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilia\PycharmProjects\WatsonInstitute\PTA\Truist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00C7608-4A07-4D02-80D5-7BE82DEB239B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104F3EB3-84B5-4491-BFE5-708F3501A1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="1155" windowWidth="25320" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="1065" windowWidth="23055" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Contact ID</t>
   </si>
@@ -65,6 +65,18 @@
   </si>
   <si>
     <t>12-08-2025</t>
+  </si>
+  <si>
+    <t>0033h0000187EiY</t>
+  </si>
+  <si>
+    <t>Sahadia</t>
+  </si>
+  <si>
+    <t>Auguste</t>
+  </si>
+  <si>
+    <t>sahadia.auguste@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -427,13 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" customWidth="1"/>
     <col min="5" max="5" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,6 +500,23 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
